--- a/excel/500(n)/RAW_Dataset.xlsx
+++ b/excel/500(n)/RAW_Dataset.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\#Java-Practice\##SS2\Lab3 Sorting\excel\"/>
     </mc:Choice>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
   <si>
     <t xml:space="preserve">Algorithm </t>
   </si>
@@ -58,12 +58,316 @@
   </si>
   <si>
     <t>Trial 9</t>
+  </si>
+  <si>
+    <t>Bubble Sort</t>
+  </si>
+  <si>
+    <t>Bubble Sort (Reverse)</t>
+  </si>
+  <si>
+    <t>Insertion Sort</t>
+  </si>
+  <si>
+    <t>Insertion Sort (Reverse)</t>
+  </si>
+  <si>
+    <t>Selection Sort</t>
+  </si>
+  <si>
+    <t>Selection Sort (Reverse)</t>
+  </si>
+  <si>
+    <t>Merge Sort</t>
+  </si>
+  <si>
+    <t>Merge Sort (Reverse)</t>
+  </si>
+  <si>
+    <t>Quick Sort</t>
+  </si>
+  <si>
+    <t>Quick Sort (Reverse)</t>
+  </si>
+  <si>
+    <t>Trial 10</t>
+  </si>
+  <si>
+    <t>Trial 11</t>
+  </si>
+  <si>
+    <t>Trial 12</t>
+  </si>
+  <si>
+    <t>Trial 13</t>
+  </si>
+  <si>
+    <t>Trial 14</t>
+  </si>
+  <si>
+    <t>Trial 15</t>
+  </si>
+  <si>
+    <t>Trial 16</t>
+  </si>
+  <si>
+    <t>Trial 17</t>
+  </si>
+  <si>
+    <t>Trial 18</t>
+  </si>
+  <si>
+    <t>Trial 19</t>
+  </si>
+  <si>
+    <t>Trial 20</t>
+  </si>
+  <si>
+    <t>Trial 21</t>
+  </si>
+  <si>
+    <t>Trial 22</t>
+  </si>
+  <si>
+    <t>Trial 23</t>
+  </si>
+  <si>
+    <t>Trial 24</t>
+  </si>
+  <si>
+    <t>Trial 25</t>
+  </si>
+  <si>
+    <t>Trial 26</t>
+  </si>
+  <si>
+    <t>Trial 27</t>
+  </si>
+  <si>
+    <t>Trial 28</t>
+  </si>
+  <si>
+    <t>Trial 29</t>
+  </si>
+  <si>
+    <t>Trial 30</t>
+  </si>
+  <si>
+    <t>Trial 31</t>
+  </si>
+  <si>
+    <t>Trial 32</t>
+  </si>
+  <si>
+    <t>Trial 33</t>
+  </si>
+  <si>
+    <t>Trial 34</t>
+  </si>
+  <si>
+    <t>Trial 35</t>
+  </si>
+  <si>
+    <t>Trial 36</t>
+  </si>
+  <si>
+    <t>Trial 37</t>
+  </si>
+  <si>
+    <t>Trial 38</t>
+  </si>
+  <si>
+    <t>Trial 39</t>
+  </si>
+  <si>
+    <t>Trial 40</t>
+  </si>
+  <si>
+    <t>Trial 41</t>
+  </si>
+  <si>
+    <t>Trial 42</t>
+  </si>
+  <si>
+    <t>Trial 43</t>
+  </si>
+  <si>
+    <t>Trial 44</t>
+  </si>
+  <si>
+    <t>Trial 45</t>
+  </si>
+  <si>
+    <t>Trial 46</t>
+  </si>
+  <si>
+    <t>Trial 47</t>
+  </si>
+  <si>
+    <t>Trial 48</t>
+  </si>
+  <si>
+    <t>Trial 49</t>
+  </si>
+  <si>
+    <t>Trial 50</t>
+  </si>
+  <si>
+    <t>Trial 51</t>
+  </si>
+  <si>
+    <t>Trial 52</t>
+  </si>
+  <si>
+    <t>Trial 53</t>
+  </si>
+  <si>
+    <t>Trial 54</t>
+  </si>
+  <si>
+    <t>Trial 55</t>
+  </si>
+  <si>
+    <t>Trial 56</t>
+  </si>
+  <si>
+    <t>Trial 57</t>
+  </si>
+  <si>
+    <t>Trial 58</t>
+  </si>
+  <si>
+    <t>Trial 59</t>
+  </si>
+  <si>
+    <t>Trial 60</t>
+  </si>
+  <si>
+    <t>Trial 61</t>
+  </si>
+  <si>
+    <t>Trial 62</t>
+  </si>
+  <si>
+    <t>Trial 63</t>
+  </si>
+  <si>
+    <t>Trial 64</t>
+  </si>
+  <si>
+    <t>Trial 65</t>
+  </si>
+  <si>
+    <t>Trial 66</t>
+  </si>
+  <si>
+    <t>Trial 67</t>
+  </si>
+  <si>
+    <t>Trial 68</t>
+  </si>
+  <si>
+    <t>Trial 69</t>
+  </si>
+  <si>
+    <t>Trial 70</t>
+  </si>
+  <si>
+    <t>Trial 71</t>
+  </si>
+  <si>
+    <t>Trial 72</t>
+  </si>
+  <si>
+    <t>Trial 73</t>
+  </si>
+  <si>
+    <t>Trial 74</t>
+  </si>
+  <si>
+    <t>Trial 75</t>
+  </si>
+  <si>
+    <t>Trial 76</t>
+  </si>
+  <si>
+    <t>Trial 77</t>
+  </si>
+  <si>
+    <t>Trial 78</t>
+  </si>
+  <si>
+    <t>Trial 79</t>
+  </si>
+  <si>
+    <t>Trial 80</t>
+  </si>
+  <si>
+    <t>Trial 81</t>
+  </si>
+  <si>
+    <t>Trial 82</t>
+  </si>
+  <si>
+    <t>Trial 83</t>
+  </si>
+  <si>
+    <t>Trial 84</t>
+  </si>
+  <si>
+    <t>Trial 85</t>
+  </si>
+  <si>
+    <t>Trial 86</t>
+  </si>
+  <si>
+    <t>Trial 87</t>
+  </si>
+  <si>
+    <t>Trial 88</t>
+  </si>
+  <si>
+    <t>Trial 89</t>
+  </si>
+  <si>
+    <t>Trial 90</t>
+  </si>
+  <si>
+    <t>Trial 91</t>
+  </si>
+  <si>
+    <t>Trial 92</t>
+  </si>
+  <si>
+    <t>Trial 93</t>
+  </si>
+  <si>
+    <t>Trial 94</t>
+  </si>
+  <si>
+    <t>Trial 95</t>
+  </si>
+  <si>
+    <t>Trial 96</t>
+  </si>
+  <si>
+    <t>Trial 97</t>
+  </si>
+  <si>
+    <t>Trial 98</t>
+  </si>
+  <si>
+    <t>Trial 99</t>
+  </si>
+  <si>
+    <t>Trial 100</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -388,11 +692,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:CX11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.77734375" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="14.77734375"/>
+    <col min="2" max="2" customWidth="true" width="13.33203125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.5">
@@ -402,32 +706,3385 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" t="s" s="0">
         <v>10</v>
+      </c>
+      <c r="L1" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M1" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="P1" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="Q1" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="R1" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="S1" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="T1" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="U1" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="V1" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="W1" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="X1" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="Y1" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="Z1" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="AA1" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="AB1" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="AC1" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="AD1" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="AE1" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="AF1" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="AG1" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="AH1" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="AI1" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="AJ1" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="AK1" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="AL1" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="AM1" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="AN1" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="AO1" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="AP1" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="AQ1" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="AR1" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="AS1" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="AT1" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="AU1" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="AV1" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="AW1" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="AX1" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="AY1" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="AZ1" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="BA1" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="BB1" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="BC1" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="BD1" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="BE1" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="BF1" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="BG1" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="BH1" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="BI1" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="BJ1" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="BK1" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="BL1" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="BM1" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="BN1" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="BO1" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="BP1" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="BQ1" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="BR1" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="BS1" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="BT1" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="BU1" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="BV1" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="BW1" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="BX1" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="BY1" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="BZ1" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="CA1" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="CB1" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="CC1" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="CD1" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="CE1" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="CF1" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="CG1" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="CH1" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="CI1" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="CJ1" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="CK1" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="CL1" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="CM1" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="CN1" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="CO1" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="CP1" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="CQ1" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="CR1" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="CS1" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="CT1" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="CU1" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="CV1" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="CW1" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="CX1" t="s" s="0">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="B2" t="n" s="0">
+        <v>500.0</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>1947300.0</v>
+      </c>
+      <c r="D2" t="n" s="0">
+        <v>629300.0</v>
+      </c>
+      <c r="E2" t="n" s="0">
+        <v>345400.0</v>
+      </c>
+      <c r="F2" t="n" s="0">
+        <v>196100.0</v>
+      </c>
+      <c r="G2" t="n" s="0">
+        <v>284300.0</v>
+      </c>
+      <c r="H2" t="n" s="0">
+        <v>295400.0</v>
+      </c>
+      <c r="I2" t="n" s="0">
+        <v>213200.0</v>
+      </c>
+      <c r="J2" t="n" s="0">
+        <v>340300.0</v>
+      </c>
+      <c r="K2" t="n" s="0">
+        <v>189900.0</v>
+      </c>
+      <c r="L2" t="n" s="0">
+        <v>178900.0</v>
+      </c>
+      <c r="M2" t="n" s="0">
+        <v>229200.0</v>
+      </c>
+      <c r="N2" t="n" s="0">
+        <v>183300.0</v>
+      </c>
+      <c r="O2" t="n" s="0">
+        <v>376700.0</v>
+      </c>
+      <c r="P2" t="n" s="0">
+        <v>332000.0</v>
+      </c>
+      <c r="Q2" t="n" s="0">
+        <v>182600.0</v>
+      </c>
+      <c r="R2" t="n" s="0">
+        <v>181200.0</v>
+      </c>
+      <c r="S2" t="n" s="0">
+        <v>183600.0</v>
+      </c>
+      <c r="T2" t="n" s="0">
+        <v>240000.0</v>
+      </c>
+      <c r="U2" t="n" s="0">
+        <v>179200.0</v>
+      </c>
+      <c r="V2" t="n" s="0">
+        <v>176500.0</v>
+      </c>
+      <c r="W2" t="n" s="0">
+        <v>193300.0</v>
+      </c>
+      <c r="X2" t="n" s="0">
+        <v>179200.0</v>
+      </c>
+      <c r="Y2" t="n" s="0">
+        <v>177800.0</v>
+      </c>
+      <c r="Z2" t="n" s="0">
+        <v>180900.0</v>
+      </c>
+      <c r="AA2" t="n" s="0">
+        <v>182600.0</v>
+      </c>
+      <c r="AB2" t="n" s="0">
+        <v>179900.0</v>
+      </c>
+      <c r="AC2" t="n" s="0">
+        <v>194500.0</v>
+      </c>
+      <c r="AD2" t="n" s="0">
+        <v>259200.0</v>
+      </c>
+      <c r="AE2" t="n" s="0">
+        <v>372100.0</v>
+      </c>
+      <c r="AF2" t="n" s="0">
+        <v>315900.0</v>
+      </c>
+      <c r="AG2" t="n" s="0">
+        <v>302900.0</v>
+      </c>
+      <c r="AH2" t="n" s="0">
+        <v>235600.0</v>
+      </c>
+      <c r="AI2" t="n" s="0">
+        <v>232400.0</v>
+      </c>
+      <c r="AJ2" t="n" s="0">
+        <v>327700.0</v>
+      </c>
+      <c r="AK2" t="n" s="0">
+        <v>179100.0</v>
+      </c>
+      <c r="AL2" t="n" s="0">
+        <v>186300.0</v>
+      </c>
+      <c r="AM2" t="n" s="0">
+        <v>184400.0</v>
+      </c>
+      <c r="AN2" t="n" s="0">
+        <v>202900.0</v>
+      </c>
+      <c r="AO2" t="n" s="0">
+        <v>187800.0</v>
+      </c>
+      <c r="AP2" t="n" s="0">
+        <v>178500.0</v>
+      </c>
+      <c r="AQ2" t="n" s="0">
+        <v>182400.0</v>
+      </c>
+      <c r="AR2" t="n" s="0">
+        <v>185500.0</v>
+      </c>
+      <c r="AS2" t="n" s="0">
+        <v>202700.0</v>
+      </c>
+      <c r="AT2" t="n" s="0">
+        <v>175900.0</v>
+      </c>
+      <c r="AU2" t="n" s="0">
+        <v>193700.0</v>
+      </c>
+      <c r="AV2" t="n" s="0">
+        <v>170000.0</v>
+      </c>
+      <c r="AW2" t="n" s="0">
+        <v>195200.0</v>
+      </c>
+      <c r="AX2" t="n" s="0">
+        <v>177000.0</v>
+      </c>
+      <c r="AY2" t="n" s="0">
+        <v>184800.0</v>
+      </c>
+      <c r="AZ2" t="n" s="0">
+        <v>187000.0</v>
+      </c>
+      <c r="BA2" t="n" s="0">
+        <v>185900.0</v>
+      </c>
+      <c r="BB2" t="n" s="0">
+        <v>184100.0</v>
+      </c>
+      <c r="BC2" t="n" s="0">
+        <v>178700.0</v>
+      </c>
+      <c r="BD2" t="n" s="0">
+        <v>184700.0</v>
+      </c>
+      <c r="BE2" t="n" s="0">
+        <v>176400.0</v>
+      </c>
+      <c r="BF2" t="n" s="0">
+        <v>180700.0</v>
+      </c>
+      <c r="BG2" t="n" s="0">
+        <v>199600.0</v>
+      </c>
+      <c r="BH2" t="n" s="0">
+        <v>181000.0</v>
+      </c>
+      <c r="BI2" t="n" s="0">
+        <v>186800.0</v>
+      </c>
+      <c r="BJ2" t="n" s="0">
+        <v>187700.0</v>
+      </c>
+      <c r="BK2" t="n" s="0">
+        <v>177800.0</v>
+      </c>
+      <c r="BL2" t="n" s="0">
+        <v>183300.0</v>
+      </c>
+      <c r="BM2" t="n" s="0">
+        <v>184800.0</v>
+      </c>
+      <c r="BN2" t="n" s="0">
+        <v>181800.0</v>
+      </c>
+      <c r="BO2" t="n" s="0">
+        <v>197800.0</v>
+      </c>
+      <c r="BP2" t="n" s="0">
+        <v>177900.0</v>
+      </c>
+      <c r="BQ2" t="n" s="0">
+        <v>177000.0</v>
+      </c>
+      <c r="BR2" t="n" s="0">
+        <v>181600.0</v>
+      </c>
+      <c r="BS2" t="n" s="0">
+        <v>183400.0</v>
+      </c>
+      <c r="BT2" t="n" s="0">
+        <v>203400.0</v>
+      </c>
+      <c r="BU2" t="n" s="0">
+        <v>199900.0</v>
+      </c>
+      <c r="BV2" t="n" s="0">
+        <v>182600.0</v>
+      </c>
+      <c r="BW2" t="n" s="0">
+        <v>183400.0</v>
+      </c>
+      <c r="BX2" t="n" s="0">
+        <v>180900.0</v>
+      </c>
+      <c r="BY2" t="n" s="0">
+        <v>246200.0</v>
+      </c>
+      <c r="BZ2" t="n" s="0">
+        <v>180100.0</v>
+      </c>
+      <c r="CA2" t="n" s="0">
+        <v>187200.0</v>
+      </c>
+      <c r="CB2" t="n" s="0">
+        <v>173500.0</v>
+      </c>
+      <c r="CC2" t="n" s="0">
+        <v>180100.0</v>
+      </c>
+      <c r="CD2" t="n" s="0">
+        <v>176900.0</v>
+      </c>
+      <c r="CE2" t="n" s="0">
+        <v>187800.0</v>
+      </c>
+      <c r="CF2" t="n" s="0">
+        <v>178700.0</v>
+      </c>
+      <c r="CG2" t="n" s="0">
+        <v>187100.0</v>
+      </c>
+      <c r="CH2" t="n" s="0">
+        <v>180300.0</v>
+      </c>
+      <c r="CI2" t="n" s="0">
+        <v>174800.0</v>
+      </c>
+      <c r="CJ2" t="n" s="0">
+        <v>175800.0</v>
+      </c>
+      <c r="CK2" t="n" s="0">
+        <v>176500.0</v>
+      </c>
+      <c r="CL2" t="n" s="0">
+        <v>178600.0</v>
+      </c>
+      <c r="CM2" t="n" s="0">
+        <v>183400.0</v>
+      </c>
+      <c r="CN2" t="n" s="0">
+        <v>178100.0</v>
+      </c>
+      <c r="CO2" t="n" s="0">
+        <v>175800.0</v>
+      </c>
+      <c r="CP2" t="n" s="0">
+        <v>188000.0</v>
+      </c>
+      <c r="CQ2" t="n" s="0">
+        <v>198400.0</v>
+      </c>
+      <c r="CR2" t="n" s="0">
+        <v>181100.0</v>
+      </c>
+      <c r="CS2" t="n" s="0">
+        <v>175500.0</v>
+      </c>
+      <c r="CT2" t="n" s="0">
+        <v>176200.0</v>
+      </c>
+      <c r="CU2" t="n" s="0">
+        <v>186000.0</v>
+      </c>
+      <c r="CV2" t="n" s="0">
+        <v>174000.0</v>
+      </c>
+      <c r="CW2" t="n" s="0">
+        <v>333100.0</v>
+      </c>
+      <c r="CX2" t="n" s="0">
+        <v>340700.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B3" t="n" s="0">
+        <v>500.0</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>1881600.0</v>
+      </c>
+      <c r="D3" t="n" s="0">
+        <v>664700.0</v>
+      </c>
+      <c r="E3" t="n" s="0">
+        <v>332900.0</v>
+      </c>
+      <c r="F3" t="n" s="0">
+        <v>228800.0</v>
+      </c>
+      <c r="G3" t="n" s="0">
+        <v>348500.0</v>
+      </c>
+      <c r="H3" t="n" s="0">
+        <v>353900.0</v>
+      </c>
+      <c r="I3" t="n" s="0">
+        <v>259100.0</v>
+      </c>
+      <c r="J3" t="n" s="0">
+        <v>351800.0</v>
+      </c>
+      <c r="K3" t="n" s="0">
+        <v>233500.0</v>
+      </c>
+      <c r="L3" t="n" s="0">
+        <v>350600.0</v>
+      </c>
+      <c r="M3" t="n" s="0">
+        <v>205300.0</v>
+      </c>
+      <c r="N3" t="n" s="0">
+        <v>195700.0</v>
+      </c>
+      <c r="O3" t="n" s="0">
+        <v>359400.0</v>
+      </c>
+      <c r="P3" t="n" s="0">
+        <v>279000.0</v>
+      </c>
+      <c r="Q3" t="n" s="0">
+        <v>211900.0</v>
+      </c>
+      <c r="R3" t="n" s="0">
+        <v>218200.0</v>
+      </c>
+      <c r="S3" t="n" s="0">
+        <v>196600.0</v>
+      </c>
+      <c r="T3" t="n" s="0">
+        <v>246000.0</v>
+      </c>
+      <c r="U3" t="n" s="0">
+        <v>223700.0</v>
+      </c>
+      <c r="V3" t="n" s="0">
+        <v>235900.0</v>
+      </c>
+      <c r="W3" t="n" s="0">
+        <v>256200.0</v>
+      </c>
+      <c r="X3" t="n" s="0">
+        <v>228900.0</v>
+      </c>
+      <c r="Y3" t="n" s="0">
+        <v>232700.0</v>
+      </c>
+      <c r="Z3" t="n" s="0">
+        <v>207500.0</v>
+      </c>
+      <c r="AA3" t="n" s="0">
+        <v>185700.0</v>
+      </c>
+      <c r="AB3" t="n" s="0">
+        <v>184100.0</v>
+      </c>
+      <c r="AC3" t="n" s="0">
+        <v>233900.0</v>
+      </c>
+      <c r="AD3" t="n" s="0">
+        <v>208000.0</v>
+      </c>
+      <c r="AE3" t="n" s="0">
+        <v>308600.0</v>
+      </c>
+      <c r="AF3" t="n" s="0">
+        <v>331400.0</v>
+      </c>
+      <c r="AG3" t="n" s="0">
+        <v>339200.0</v>
+      </c>
+      <c r="AH3" t="n" s="0">
+        <v>205400.0</v>
+      </c>
+      <c r="AI3" t="n" s="0">
+        <v>225400.0</v>
+      </c>
+      <c r="AJ3" t="n" s="0">
+        <v>345100.0</v>
+      </c>
+      <c r="AK3" t="n" s="0">
+        <v>217700.0</v>
+      </c>
+      <c r="AL3" t="n" s="0">
+        <v>214000.0</v>
+      </c>
+      <c r="AM3" t="n" s="0">
+        <v>218300.0</v>
+      </c>
+      <c r="AN3" t="n" s="0">
+        <v>218600.0</v>
+      </c>
+      <c r="AO3" t="n" s="0">
+        <v>199800.0</v>
+      </c>
+      <c r="AP3" t="n" s="0">
+        <v>208000.0</v>
+      </c>
+      <c r="AQ3" t="n" s="0">
+        <v>216100.0</v>
+      </c>
+      <c r="AR3" t="n" s="0">
+        <v>202700.0</v>
+      </c>
+      <c r="AS3" t="n" s="0">
+        <v>221200.0</v>
+      </c>
+      <c r="AT3" t="n" s="0">
+        <v>202100.0</v>
+      </c>
+      <c r="AU3" t="n" s="0">
+        <v>222200.0</v>
+      </c>
+      <c r="AV3" t="n" s="0">
+        <v>226700.0</v>
+      </c>
+      <c r="AW3" t="n" s="0">
+        <v>194500.0</v>
+      </c>
+      <c r="AX3" t="n" s="0">
+        <v>219800.0</v>
+      </c>
+      <c r="AY3" t="n" s="0">
+        <v>183400.0</v>
+      </c>
+      <c r="AZ3" t="n" s="0">
+        <v>206400.0</v>
+      </c>
+      <c r="BA3" t="n" s="0">
+        <v>206300.0</v>
+      </c>
+      <c r="BB3" t="n" s="0">
+        <v>222300.0</v>
+      </c>
+      <c r="BC3" t="n" s="0">
+        <v>187600.0</v>
+      </c>
+      <c r="BD3" t="n" s="0">
+        <v>227700.0</v>
+      </c>
+      <c r="BE3" t="n" s="0">
+        <v>221700.0</v>
+      </c>
+      <c r="BF3" t="n" s="0">
+        <v>227700.0</v>
+      </c>
+      <c r="BG3" t="n" s="0">
+        <v>195700.0</v>
+      </c>
+      <c r="BH3" t="n" s="0">
+        <v>219200.0</v>
+      </c>
+      <c r="BI3" t="n" s="0">
+        <v>203200.0</v>
+      </c>
+      <c r="BJ3" t="n" s="0">
+        <v>215500.0</v>
+      </c>
+      <c r="BK3" t="n" s="0">
+        <v>189400.0</v>
+      </c>
+      <c r="BL3" t="n" s="0">
+        <v>219100.0</v>
+      </c>
+      <c r="BM3" t="n" s="0">
+        <v>196900.0</v>
+      </c>
+      <c r="BN3" t="n" s="0">
+        <v>243000.0</v>
+      </c>
+      <c r="BO3" t="n" s="0">
+        <v>346400.0</v>
+      </c>
+      <c r="BP3" t="n" s="0">
+        <v>233100.0</v>
+      </c>
+      <c r="BQ3" t="n" s="0">
+        <v>223400.0</v>
+      </c>
+      <c r="BR3" t="n" s="0">
+        <v>305200.0</v>
+      </c>
+      <c r="BS3" t="n" s="0">
+        <v>234800.0</v>
+      </c>
+      <c r="BT3" t="n" s="0">
+        <v>479100.0</v>
+      </c>
+      <c r="BU3" t="n" s="0">
+        <v>358800.0</v>
+      </c>
+      <c r="BV3" t="n" s="0">
+        <v>205500.0</v>
+      </c>
+      <c r="BW3" t="n" s="0">
+        <v>230700.0</v>
+      </c>
+      <c r="BX3" t="n" s="0">
+        <v>221900.0</v>
+      </c>
+      <c r="BY3" t="n" s="0">
+        <v>206100.0</v>
+      </c>
+      <c r="BZ3" t="n" s="0">
+        <v>216400.0</v>
+      </c>
+      <c r="CA3" t="n" s="0">
+        <v>206100.0</v>
+      </c>
+      <c r="CB3" t="n" s="0">
+        <v>200400.0</v>
+      </c>
+      <c r="CC3" t="n" s="0">
+        <v>210500.0</v>
+      </c>
+      <c r="CD3" t="n" s="0">
+        <v>216400.0</v>
+      </c>
+      <c r="CE3" t="n" s="0">
+        <v>210400.0</v>
+      </c>
+      <c r="CF3" t="n" s="0">
+        <v>233000.0</v>
+      </c>
+      <c r="CG3" t="n" s="0">
+        <v>193000.0</v>
+      </c>
+      <c r="CH3" t="n" s="0">
+        <v>217000.0</v>
+      </c>
+      <c r="CI3" t="n" s="0">
+        <v>212200.0</v>
+      </c>
+      <c r="CJ3" t="n" s="0">
+        <v>223300.0</v>
+      </c>
+      <c r="CK3" t="n" s="0">
+        <v>224500.0</v>
+      </c>
+      <c r="CL3" t="n" s="0">
+        <v>225200.0</v>
+      </c>
+      <c r="CM3" t="n" s="0">
+        <v>236000.0</v>
+      </c>
+      <c r="CN3" t="n" s="0">
+        <v>193400.0</v>
+      </c>
+      <c r="CO3" t="n" s="0">
+        <v>196900.0</v>
+      </c>
+      <c r="CP3" t="n" s="0">
+        <v>201800.0</v>
+      </c>
+      <c r="CQ3" t="n" s="0">
+        <v>218500.0</v>
+      </c>
+      <c r="CR3" t="n" s="0">
+        <v>222300.0</v>
+      </c>
+      <c r="CS3" t="n" s="0">
+        <v>232300.0</v>
+      </c>
+      <c r="CT3" t="n" s="0">
+        <v>229000.0</v>
+      </c>
+      <c r="CU3" t="n" s="0">
+        <v>221900.0</v>
+      </c>
+      <c r="CV3" t="n" s="0">
+        <v>199000.0</v>
+      </c>
+      <c r="CW3" t="n" s="0">
+        <v>344600.0</v>
+      </c>
+      <c r="CX3" t="n" s="0">
+        <v>350400.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="B4" t="n" s="0">
+        <v>500.0</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>1049700.0</v>
+      </c>
+      <c r="D4" t="n" s="0">
+        <v>327700.0</v>
+      </c>
+      <c r="E4" t="n" s="0">
+        <v>132400.0</v>
+      </c>
+      <c r="F4" t="n" s="0">
+        <v>110100.0</v>
+      </c>
+      <c r="G4" t="n" s="0">
+        <v>29000.0</v>
+      </c>
+      <c r="H4" t="n" s="0">
+        <v>27600.0</v>
+      </c>
+      <c r="I4" t="n" s="0">
+        <v>22500.0</v>
+      </c>
+      <c r="J4" t="n" s="0">
+        <v>27800.0</v>
+      </c>
+      <c r="K4" t="n" s="0">
+        <v>15600.0</v>
+      </c>
+      <c r="L4" t="n" s="0">
+        <v>26800.0</v>
+      </c>
+      <c r="M4" t="n" s="0">
+        <v>16300.0</v>
+      </c>
+      <c r="N4" t="n" s="0">
+        <v>15600.0</v>
+      </c>
+      <c r="O4" t="n" s="0">
+        <v>28800.0</v>
+      </c>
+      <c r="P4" t="n" s="0">
+        <v>30300.0</v>
+      </c>
+      <c r="Q4" t="n" s="0">
+        <v>15600.0</v>
+      </c>
+      <c r="R4" t="n" s="0">
+        <v>14900.0</v>
+      </c>
+      <c r="S4" t="n" s="0">
+        <v>15100.0</v>
+      </c>
+      <c r="T4" t="n" s="0">
+        <v>23500.0</v>
+      </c>
+      <c r="U4" t="n" s="0">
+        <v>15400.0</v>
+      </c>
+      <c r="V4" t="n" s="0">
+        <v>15800.0</v>
+      </c>
+      <c r="W4" t="n" s="0">
+        <v>15600.0</v>
+      </c>
+      <c r="X4" t="n" s="0">
+        <v>14900.0</v>
+      </c>
+      <c r="Y4" t="n" s="0">
+        <v>15200.0</v>
+      </c>
+      <c r="Z4" t="n" s="0">
+        <v>15300.0</v>
+      </c>
+      <c r="AA4" t="n" s="0">
+        <v>15300.0</v>
+      </c>
+      <c r="AB4" t="n" s="0">
+        <v>15300.0</v>
+      </c>
+      <c r="AC4" t="n" s="0">
+        <v>15300.0</v>
+      </c>
+      <c r="AD4" t="n" s="0">
+        <v>15100.0</v>
+      </c>
+      <c r="AE4" t="n" s="0">
+        <v>27000.0</v>
+      </c>
+      <c r="AF4" t="n" s="0">
+        <v>27400.0</v>
+      </c>
+      <c r="AG4" t="n" s="0">
+        <v>27700.0</v>
+      </c>
+      <c r="AH4" t="n" s="0">
+        <v>15100.0</v>
+      </c>
+      <c r="AI4" t="n" s="0">
+        <v>15700.0</v>
+      </c>
+      <c r="AJ4" t="n" s="0">
+        <v>27500.0</v>
+      </c>
+      <c r="AK4" t="n" s="0">
+        <v>16300.0</v>
+      </c>
+      <c r="AL4" t="n" s="0">
+        <v>17000.0</v>
+      </c>
+      <c r="AM4" t="n" s="0">
+        <v>15800.0</v>
+      </c>
+      <c r="AN4" t="n" s="0">
+        <v>20200.0</v>
+      </c>
+      <c r="AO4" t="n" s="0">
+        <v>19000.0</v>
+      </c>
+      <c r="AP4" t="n" s="0">
+        <v>15400.0</v>
+      </c>
+      <c r="AQ4" t="n" s="0">
+        <v>14800.0</v>
+      </c>
+      <c r="AR4" t="n" s="0">
+        <v>15100.0</v>
+      </c>
+      <c r="AS4" t="n" s="0">
+        <v>15800.0</v>
+      </c>
+      <c r="AT4" t="n" s="0">
+        <v>14400.0</v>
+      </c>
+      <c r="AU4" t="n" s="0">
+        <v>15600.0</v>
+      </c>
+      <c r="AV4" t="n" s="0">
+        <v>14500.0</v>
+      </c>
+      <c r="AW4" t="n" s="0">
+        <v>15400.0</v>
+      </c>
+      <c r="AX4" t="n" s="0">
+        <v>14900.0</v>
+      </c>
+      <c r="AY4" t="n" s="0">
+        <v>15000.0</v>
+      </c>
+      <c r="AZ4" t="n" s="0">
+        <v>18600.0</v>
+      </c>
+      <c r="BA4" t="n" s="0">
+        <v>15700.0</v>
+      </c>
+      <c r="BB4" t="n" s="0">
+        <v>15800.0</v>
+      </c>
+      <c r="BC4" t="n" s="0">
+        <v>15000.0</v>
+      </c>
+      <c r="BD4" t="n" s="0">
+        <v>15300.0</v>
+      </c>
+      <c r="BE4" t="n" s="0">
+        <v>14400.0</v>
+      </c>
+      <c r="BF4" t="n" s="0">
+        <v>17900.0</v>
+      </c>
+      <c r="BG4" t="n" s="0">
+        <v>16200.0</v>
+      </c>
+      <c r="BH4" t="n" s="0">
+        <v>15400.0</v>
+      </c>
+      <c r="BI4" t="n" s="0">
+        <v>15300.0</v>
+      </c>
+      <c r="BJ4" t="n" s="0">
+        <v>16300.0</v>
+      </c>
+      <c r="BK4" t="n" s="0">
+        <v>15300.0</v>
+      </c>
+      <c r="BL4" t="n" s="0">
+        <v>14800.0</v>
+      </c>
+      <c r="BM4" t="n" s="0">
+        <v>18500.0</v>
+      </c>
+      <c r="BN4" t="n" s="0">
+        <v>14600.0</v>
+      </c>
+      <c r="BO4" t="n" s="0">
+        <v>35400.0</v>
+      </c>
+      <c r="BP4" t="n" s="0">
+        <v>45500.0</v>
+      </c>
+      <c r="BQ4" t="n" s="0">
+        <v>15200.0</v>
+      </c>
+      <c r="BR4" t="n" s="0">
+        <v>17700.0</v>
+      </c>
+      <c r="BS4" t="n" s="0">
+        <v>15500.0</v>
+      </c>
+      <c r="BT4" t="n" s="0">
+        <v>17200.0</v>
+      </c>
+      <c r="BU4" t="n" s="0">
+        <v>35800.0</v>
+      </c>
+      <c r="BV4" t="n" s="0">
+        <v>15300.0</v>
+      </c>
+      <c r="BW4" t="n" s="0">
+        <v>15600.0</v>
+      </c>
+      <c r="BX4" t="n" s="0">
+        <v>15600.0</v>
+      </c>
+      <c r="BY4" t="n" s="0">
+        <v>15700.0</v>
+      </c>
+      <c r="BZ4" t="n" s="0">
+        <v>15300.0</v>
+      </c>
+      <c r="CA4" t="n" s="0">
+        <v>15700.0</v>
+      </c>
+      <c r="CB4" t="n" s="0">
+        <v>15200.0</v>
+      </c>
+      <c r="CC4" t="n" s="0">
+        <v>14900.0</v>
+      </c>
+      <c r="CD4" t="n" s="0">
+        <v>14900.0</v>
+      </c>
+      <c r="CE4" t="n" s="0">
+        <v>15200.0</v>
+      </c>
+      <c r="CF4" t="n" s="0">
+        <v>14900.0</v>
+      </c>
+      <c r="CG4" t="n" s="0">
+        <v>19800.0</v>
+      </c>
+      <c r="CH4" t="n" s="0">
+        <v>14800.0</v>
+      </c>
+      <c r="CI4" t="n" s="0">
+        <v>15600.0</v>
+      </c>
+      <c r="CJ4" t="n" s="0">
+        <v>15600.0</v>
+      </c>
+      <c r="CK4" t="n" s="0">
+        <v>15000.0</v>
+      </c>
+      <c r="CL4" t="n" s="0">
+        <v>14500.0</v>
+      </c>
+      <c r="CM4" t="n" s="0">
+        <v>14800.0</v>
+      </c>
+      <c r="CN4" t="n" s="0">
+        <v>15200.0</v>
+      </c>
+      <c r="CO4" t="n" s="0">
+        <v>14900.0</v>
+      </c>
+      <c r="CP4" t="n" s="0">
+        <v>15000.0</v>
+      </c>
+      <c r="CQ4" t="n" s="0">
+        <v>15000.0</v>
+      </c>
+      <c r="CR4" t="n" s="0">
+        <v>14700.0</v>
+      </c>
+      <c r="CS4" t="n" s="0">
+        <v>14800.0</v>
+      </c>
+      <c r="CT4" t="n" s="0">
+        <v>14800.0</v>
+      </c>
+      <c r="CU4" t="n" s="0">
+        <v>15500.0</v>
+      </c>
+      <c r="CV4" t="n" s="0">
+        <v>15700.0</v>
+      </c>
+      <c r="CW4" t="n" s="0">
+        <v>26500.0</v>
+      </c>
+      <c r="CX4" t="n" s="0">
+        <v>27600.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="B5" t="n" s="0">
+        <v>500.0</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>849900.0</v>
+      </c>
+      <c r="D5" t="n" s="0">
+        <v>633900.0</v>
+      </c>
+      <c r="E5" t="n" s="0">
+        <v>229500.0</v>
+      </c>
+      <c r="F5" t="n" s="0">
+        <v>82300.0</v>
+      </c>
+      <c r="G5" t="n" s="0">
+        <v>150500.0</v>
+      </c>
+      <c r="H5" t="n" s="0">
+        <v>29600.0</v>
+      </c>
+      <c r="I5" t="n" s="0">
+        <v>23800.0</v>
+      </c>
+      <c r="J5" t="n" s="0">
+        <v>42600.0</v>
+      </c>
+      <c r="K5" t="n" s="0">
+        <v>15300.0</v>
+      </c>
+      <c r="L5" t="n" s="0">
+        <v>28500.0</v>
+      </c>
+      <c r="M5" t="n" s="0">
+        <v>15500.0</v>
+      </c>
+      <c r="N5" t="n" s="0">
+        <v>14100.0</v>
+      </c>
+      <c r="O5" t="n" s="0">
+        <v>28600.0</v>
+      </c>
+      <c r="P5" t="n" s="0">
+        <v>30700.0</v>
+      </c>
+      <c r="Q5" t="n" s="0">
+        <v>14000.0</v>
+      </c>
+      <c r="R5" t="n" s="0">
+        <v>14700.0</v>
+      </c>
+      <c r="S5" t="n" s="0">
+        <v>14200.0</v>
+      </c>
+      <c r="T5" t="n" s="0">
+        <v>19900.0</v>
+      </c>
+      <c r="U5" t="n" s="0">
+        <v>14200.0</v>
+      </c>
+      <c r="V5" t="n" s="0">
+        <v>14300.0</v>
+      </c>
+      <c r="W5" t="n" s="0">
+        <v>14800.0</v>
+      </c>
+      <c r="X5" t="n" s="0">
+        <v>14800.0</v>
+      </c>
+      <c r="Y5" t="n" s="0">
+        <v>14800.0</v>
+      </c>
+      <c r="Z5" t="n" s="0">
+        <v>15200.0</v>
+      </c>
+      <c r="AA5" t="n" s="0">
+        <v>15100.0</v>
+      </c>
+      <c r="AB5" t="n" s="0">
+        <v>14700.0</v>
+      </c>
+      <c r="AC5" t="n" s="0">
+        <v>14300.0</v>
+      </c>
+      <c r="AD5" t="n" s="0">
+        <v>15100.0</v>
+      </c>
+      <c r="AE5" t="n" s="0">
+        <v>29200.0</v>
+      </c>
+      <c r="AF5" t="n" s="0">
+        <v>26200.0</v>
+      </c>
+      <c r="AG5" t="n" s="0">
+        <v>26500.0</v>
+      </c>
+      <c r="AH5" t="n" s="0">
+        <v>16000.0</v>
+      </c>
+      <c r="AI5" t="n" s="0">
+        <v>15100.0</v>
+      </c>
+      <c r="AJ5" t="n" s="0">
+        <v>26800.0</v>
+      </c>
+      <c r="AK5" t="n" s="0">
+        <v>14600.0</v>
+      </c>
+      <c r="AL5" t="n" s="0">
+        <v>14700.0</v>
+      </c>
+      <c r="AM5" t="n" s="0">
+        <v>14200.0</v>
+      </c>
+      <c r="AN5" t="n" s="0">
+        <v>19900.0</v>
+      </c>
+      <c r="AO5" t="n" s="0">
+        <v>17300.0</v>
+      </c>
+      <c r="AP5" t="n" s="0">
+        <v>14700.0</v>
+      </c>
+      <c r="AQ5" t="n" s="0">
+        <v>14700.0</v>
+      </c>
+      <c r="AR5" t="n" s="0">
+        <v>14300.0</v>
+      </c>
+      <c r="AS5" t="n" s="0">
+        <v>16000.0</v>
+      </c>
+      <c r="AT5" t="n" s="0">
+        <v>14900.0</v>
+      </c>
+      <c r="AU5" t="n" s="0">
+        <v>14600.0</v>
+      </c>
+      <c r="AV5" t="n" s="0">
+        <v>14800.0</v>
+      </c>
+      <c r="AW5" t="n" s="0">
+        <v>14100.0</v>
+      </c>
+      <c r="AX5" t="n" s="0">
+        <v>14700.0</v>
+      </c>
+      <c r="AY5" t="n" s="0">
+        <v>14300.0</v>
+      </c>
+      <c r="AZ5" t="n" s="0">
+        <v>17100.0</v>
+      </c>
+      <c r="BA5" t="n" s="0">
+        <v>14100.0</v>
+      </c>
+      <c r="BB5" t="n" s="0">
+        <v>14900.0</v>
+      </c>
+      <c r="BC5" t="n" s="0">
+        <v>14300.0</v>
+      </c>
+      <c r="BD5" t="n" s="0">
+        <v>13900.0</v>
+      </c>
+      <c r="BE5" t="n" s="0">
+        <v>14900.0</v>
+      </c>
+      <c r="BF5" t="n" s="0">
+        <v>24600.0</v>
+      </c>
+      <c r="BG5" t="n" s="0">
+        <v>15500.0</v>
+      </c>
+      <c r="BH5" t="n" s="0">
+        <v>15000.0</v>
+      </c>
+      <c r="BI5" t="n" s="0">
+        <v>14300.0</v>
+      </c>
+      <c r="BJ5" t="n" s="0">
+        <v>14100.0</v>
+      </c>
+      <c r="BK5" t="n" s="0">
+        <v>14100.0</v>
+      </c>
+      <c r="BL5" t="n" s="0">
+        <v>14300.0</v>
+      </c>
+      <c r="BM5" t="n" s="0">
+        <v>14000.0</v>
+      </c>
+      <c r="BN5" t="n" s="0">
+        <v>15000.0</v>
+      </c>
+      <c r="BO5" t="n" s="0">
+        <v>27200.0</v>
+      </c>
+      <c r="BP5" t="n" s="0">
+        <v>15500.0</v>
+      </c>
+      <c r="BQ5" t="n" s="0">
+        <v>15800.0</v>
+      </c>
+      <c r="BR5" t="n" s="0">
+        <v>17000.0</v>
+      </c>
+      <c r="BS5" t="n" s="0">
+        <v>14400.0</v>
+      </c>
+      <c r="BT5" t="n" s="0">
+        <v>15900.0</v>
+      </c>
+      <c r="BU5" t="n" s="0">
+        <v>15100.0</v>
+      </c>
+      <c r="BV5" t="n" s="0">
+        <v>15000.0</v>
+      </c>
+      <c r="BW5" t="n" s="0">
+        <v>13900.0</v>
+      </c>
+      <c r="BX5" t="n" s="0">
+        <v>14200.0</v>
+      </c>
+      <c r="BY5" t="n" s="0">
+        <v>14000.0</v>
+      </c>
+      <c r="BZ5" t="n" s="0">
+        <v>14300.0</v>
+      </c>
+      <c r="CA5" t="n" s="0">
+        <v>14000.0</v>
+      </c>
+      <c r="CB5" t="n" s="0">
+        <v>18500.0</v>
+      </c>
+      <c r="CC5" t="n" s="0">
+        <v>14900.0</v>
+      </c>
+      <c r="CD5" t="n" s="0">
+        <v>14800.0</v>
+      </c>
+      <c r="CE5" t="n" s="0">
+        <v>14100.0</v>
+      </c>
+      <c r="CF5" t="n" s="0">
+        <v>14600.0</v>
+      </c>
+      <c r="CG5" t="n" s="0">
+        <v>14500.0</v>
+      </c>
+      <c r="CH5" t="n" s="0">
+        <v>14400.0</v>
+      </c>
+      <c r="CI5" t="n" s="0">
+        <v>14200.0</v>
+      </c>
+      <c r="CJ5" t="n" s="0">
+        <v>14300.0</v>
+      </c>
+      <c r="CK5" t="n" s="0">
+        <v>14700.0</v>
+      </c>
+      <c r="CL5" t="n" s="0">
+        <v>14800.0</v>
+      </c>
+      <c r="CM5" t="n" s="0">
+        <v>14600.0</v>
+      </c>
+      <c r="CN5" t="n" s="0">
+        <v>14400.0</v>
+      </c>
+      <c r="CO5" t="n" s="0">
+        <v>14700.0</v>
+      </c>
+      <c r="CP5" t="n" s="0">
+        <v>14600.0</v>
+      </c>
+      <c r="CQ5" t="n" s="0">
+        <v>14700.0</v>
+      </c>
+      <c r="CR5" t="n" s="0">
+        <v>14900.0</v>
+      </c>
+      <c r="CS5" t="n" s="0">
+        <v>14400.0</v>
+      </c>
+      <c r="CT5" t="n" s="0">
+        <v>14600.0</v>
+      </c>
+      <c r="CU5" t="n" s="0">
+        <v>15300.0</v>
+      </c>
+      <c r="CV5" t="n" s="0">
+        <v>14500.0</v>
+      </c>
+      <c r="CW5" t="n" s="0">
+        <v>35300.0</v>
+      </c>
+      <c r="CX5" t="n" s="0">
+        <v>26200.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n" s="0">
+        <v>500.0</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>722100.0</v>
+      </c>
+      <c r="D6" t="n" s="0">
+        <v>473900.0</v>
+      </c>
+      <c r="E6" t="n" s="0">
+        <v>210000.0</v>
+      </c>
+      <c r="F6" t="n" s="0">
+        <v>63300.0</v>
+      </c>
+      <c r="G6" t="n" s="0">
+        <v>120400.0</v>
+      </c>
+      <c r="H6" t="n" s="0">
+        <v>120500.0</v>
+      </c>
+      <c r="I6" t="n" s="0">
+        <v>95500.0</v>
+      </c>
+      <c r="J6" t="n" s="0">
+        <v>782000.0</v>
+      </c>
+      <c r="K6" t="n" s="0">
+        <v>65800.0</v>
+      </c>
+      <c r="L6" t="n" s="0">
+        <v>119800.0</v>
+      </c>
+      <c r="M6" t="n" s="0">
+        <v>74000.0</v>
+      </c>
+      <c r="N6" t="n" s="0">
+        <v>63200.0</v>
+      </c>
+      <c r="O6" t="n" s="0">
+        <v>121500.0</v>
+      </c>
+      <c r="P6" t="n" s="0">
+        <v>110500.0</v>
+      </c>
+      <c r="Q6" t="n" s="0">
+        <v>63200.0</v>
+      </c>
+      <c r="R6" t="n" s="0">
+        <v>62700.0</v>
+      </c>
+      <c r="S6" t="n" s="0">
+        <v>62700.0</v>
+      </c>
+      <c r="T6" t="n" s="0">
+        <v>92100.0</v>
+      </c>
+      <c r="U6" t="n" s="0">
+        <v>63200.0</v>
+      </c>
+      <c r="V6" t="n" s="0">
+        <v>62600.0</v>
+      </c>
+      <c r="W6" t="n" s="0">
+        <v>64600.0</v>
+      </c>
+      <c r="X6" t="n" s="0">
+        <v>62800.0</v>
+      </c>
+      <c r="Y6" t="n" s="0">
+        <v>61900.0</v>
+      </c>
+      <c r="Z6" t="n" s="0">
+        <v>63300.0</v>
+      </c>
+      <c r="AA6" t="n" s="0">
+        <v>63700.0</v>
+      </c>
+      <c r="AB6" t="n" s="0">
+        <v>62700.0</v>
+      </c>
+      <c r="AC6" t="n" s="0">
+        <v>63400.0</v>
+      </c>
+      <c r="AD6" t="n" s="0">
+        <v>62000.0</v>
+      </c>
+      <c r="AE6" t="n" s="0">
+        <v>120000.0</v>
+      </c>
+      <c r="AF6" t="n" s="0">
+        <v>120100.0</v>
+      </c>
+      <c r="AG6" t="n" s="0">
+        <v>131300.0</v>
+      </c>
+      <c r="AH6" t="n" s="0">
+        <v>63500.0</v>
+      </c>
+      <c r="AI6" t="n" s="0">
+        <v>63300.0</v>
+      </c>
+      <c r="AJ6" t="n" s="0">
+        <v>120600.0</v>
+      </c>
+      <c r="AK6" t="n" s="0">
+        <v>63500.0</v>
+      </c>
+      <c r="AL6" t="n" s="0">
+        <v>62300.0</v>
+      </c>
+      <c r="AM6" t="n" s="0">
+        <v>62700.0</v>
+      </c>
+      <c r="AN6" t="n" s="0">
+        <v>65700.0</v>
+      </c>
+      <c r="AO6" t="n" s="0">
+        <v>75600.0</v>
+      </c>
+      <c r="AP6" t="n" s="0">
+        <v>62100.0</v>
+      </c>
+      <c r="AQ6" t="n" s="0">
+        <v>64300.0</v>
+      </c>
+      <c r="AR6" t="n" s="0">
+        <v>63300.0</v>
+      </c>
+      <c r="AS6" t="n" s="0">
+        <v>67900.0</v>
+      </c>
+      <c r="AT6" t="n" s="0">
+        <v>63700.0</v>
+      </c>
+      <c r="AU6" t="n" s="0">
+        <v>63800.0</v>
+      </c>
+      <c r="AV6" t="n" s="0">
+        <v>61800.0</v>
+      </c>
+      <c r="AW6" t="n" s="0">
+        <v>63800.0</v>
+      </c>
+      <c r="AX6" t="n" s="0">
+        <v>63500.0</v>
+      </c>
+      <c r="AY6" t="n" s="0">
+        <v>66000.0</v>
+      </c>
+      <c r="AZ6" t="n" s="0">
+        <v>73600.0</v>
+      </c>
+      <c r="BA6" t="n" s="0">
+        <v>63000.0</v>
+      </c>
+      <c r="BB6" t="n" s="0">
+        <v>66000.0</v>
+      </c>
+      <c r="BC6" t="n" s="0">
+        <v>62900.0</v>
+      </c>
+      <c r="BD6" t="n" s="0">
+        <v>63800.0</v>
+      </c>
+      <c r="BE6" t="n" s="0">
+        <v>62800.0</v>
+      </c>
+      <c r="BF6" t="n" s="0">
+        <v>73700.0</v>
+      </c>
+      <c r="BG6" t="n" s="0">
+        <v>68300.0</v>
+      </c>
+      <c r="BH6" t="n" s="0">
+        <v>69400.0</v>
+      </c>
+      <c r="BI6" t="n" s="0">
+        <v>62400.0</v>
+      </c>
+      <c r="BJ6" t="n" s="0">
+        <v>63600.0</v>
+      </c>
+      <c r="BK6" t="n" s="0">
+        <v>62400.0</v>
+      </c>
+      <c r="BL6" t="n" s="0">
+        <v>63300.0</v>
+      </c>
+      <c r="BM6" t="n" s="0">
+        <v>62600.0</v>
+      </c>
+      <c r="BN6" t="n" s="0">
+        <v>63700.0</v>
+      </c>
+      <c r="BO6" t="n" s="0">
+        <v>120400.0</v>
+      </c>
+      <c r="BP6" t="n" s="0">
+        <v>99700.0</v>
+      </c>
+      <c r="BQ6" t="n" s="0">
+        <v>64400.0</v>
+      </c>
+      <c r="BR6" t="n" s="0">
+        <v>73800.0</v>
+      </c>
+      <c r="BS6" t="n" s="0">
+        <v>62900.0</v>
+      </c>
+      <c r="BT6" t="n" s="0">
+        <v>69700.0</v>
+      </c>
+      <c r="BU6" t="n" s="0">
+        <v>69000.0</v>
+      </c>
+      <c r="BV6" t="n" s="0">
+        <v>63900.0</v>
+      </c>
+      <c r="BW6" t="n" s="0">
+        <v>68200.0</v>
+      </c>
+      <c r="BX6" t="n" s="0">
+        <v>63400.0</v>
+      </c>
+      <c r="BY6" t="n" s="0">
+        <v>62400.0</v>
+      </c>
+      <c r="BZ6" t="n" s="0">
+        <v>62800.0</v>
+      </c>
+      <c r="CA6" t="n" s="0">
+        <v>63300.0</v>
+      </c>
+      <c r="CB6" t="n" s="0">
+        <v>62300.0</v>
+      </c>
+      <c r="CC6" t="n" s="0">
+        <v>62600.0</v>
+      </c>
+      <c r="CD6" t="n" s="0">
+        <v>62600.0</v>
+      </c>
+      <c r="CE6" t="n" s="0">
+        <v>63100.0</v>
+      </c>
+      <c r="CF6" t="n" s="0">
+        <v>62800.0</v>
+      </c>
+      <c r="CG6" t="n" s="0">
+        <v>63600.0</v>
+      </c>
+      <c r="CH6" t="n" s="0">
+        <v>61900.0</v>
+      </c>
+      <c r="CI6" t="n" s="0">
+        <v>61900.0</v>
+      </c>
+      <c r="CJ6" t="n" s="0">
+        <v>63400.0</v>
+      </c>
+      <c r="CK6" t="n" s="0">
+        <v>62400.0</v>
+      </c>
+      <c r="CL6" t="n" s="0">
+        <v>63400.0</v>
+      </c>
+      <c r="CM6" t="n" s="0">
+        <v>63200.0</v>
+      </c>
+      <c r="CN6" t="n" s="0">
+        <v>62100.0</v>
+      </c>
+      <c r="CO6" t="n" s="0">
+        <v>63300.0</v>
+      </c>
+      <c r="CP6" t="n" s="0">
+        <v>63300.0</v>
+      </c>
+      <c r="CQ6" t="n" s="0">
+        <v>62800.0</v>
+      </c>
+      <c r="CR6" t="n" s="0">
+        <v>63800.0</v>
+      </c>
+      <c r="CS6" t="n" s="0">
+        <v>62700.0</v>
+      </c>
+      <c r="CT6" t="n" s="0">
+        <v>64300.0</v>
+      </c>
+      <c r="CU6" t="n" s="0">
+        <v>64500.0</v>
+      </c>
+      <c r="CV6" t="n" s="0">
+        <v>83000.0</v>
+      </c>
+      <c r="CW6" t="n" s="0">
+        <v>160900.0</v>
+      </c>
+      <c r="CX6" t="n" s="0">
+        <v>119500.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B7" t="n" s="0">
+        <v>500.0</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>722500.0</v>
+      </c>
+      <c r="D7" t="n" s="0">
+        <v>468500.0</v>
+      </c>
+      <c r="E7" t="n" s="0">
+        <v>203300.0</v>
+      </c>
+      <c r="F7" t="n" s="0">
+        <v>63400.0</v>
+      </c>
+      <c r="G7" t="n" s="0">
+        <v>121500.0</v>
+      </c>
+      <c r="H7" t="n" s="0">
+        <v>121800.0</v>
+      </c>
+      <c r="I7" t="n" s="0">
+        <v>93300.0</v>
+      </c>
+      <c r="J7" t="n" s="0">
+        <v>78000.0</v>
+      </c>
+      <c r="K7" t="n" s="0">
+        <v>68200.0</v>
+      </c>
+      <c r="L7" t="n" s="0">
+        <v>121100.0</v>
+      </c>
+      <c r="M7" t="n" s="0">
+        <v>67500.0</v>
+      </c>
+      <c r="N7" t="n" s="0">
+        <v>335000.0</v>
+      </c>
+      <c r="O7" t="n" s="0">
+        <v>124700.0</v>
+      </c>
+      <c r="P7" t="n" s="0">
+        <v>108400.0</v>
+      </c>
+      <c r="Q7" t="n" s="0">
+        <v>71000.0</v>
+      </c>
+      <c r="R7" t="n" s="0">
+        <v>70500.0</v>
+      </c>
+      <c r="S7" t="n" s="0">
+        <v>63800.0</v>
+      </c>
+      <c r="T7" t="n" s="0">
+        <v>97200.0</v>
+      </c>
+      <c r="U7" t="n" s="0">
+        <v>62700.0</v>
+      </c>
+      <c r="V7" t="n" s="0">
+        <v>63700.0</v>
+      </c>
+      <c r="W7" t="n" s="0">
+        <v>64700.0</v>
+      </c>
+      <c r="X7" t="n" s="0">
+        <v>62400.0</v>
+      </c>
+      <c r="Y7" t="n" s="0">
+        <v>64100.0</v>
+      </c>
+      <c r="Z7" t="n" s="0">
+        <v>63400.0</v>
+      </c>
+      <c r="AA7" t="n" s="0">
+        <v>64100.0</v>
+      </c>
+      <c r="AB7" t="n" s="0">
+        <v>62900.0</v>
+      </c>
+      <c r="AC7" t="n" s="0">
+        <v>62100.0</v>
+      </c>
+      <c r="AD7" t="n" s="0">
+        <v>111300.0</v>
+      </c>
+      <c r="AE7" t="n" s="0">
+        <v>119600.0</v>
+      </c>
+      <c r="AF7" t="n" s="0">
+        <v>120200.0</v>
+      </c>
+      <c r="AG7" t="n" s="0">
+        <v>74100.0</v>
+      </c>
+      <c r="AH7" t="n" s="0">
+        <v>63500.0</v>
+      </c>
+      <c r="AI7" t="n" s="0">
+        <v>64500.0</v>
+      </c>
+      <c r="AJ7" t="n" s="0">
+        <v>120300.0</v>
+      </c>
+      <c r="AK7" t="n" s="0">
+        <v>64300.0</v>
+      </c>
+      <c r="AL7" t="n" s="0">
+        <v>63200.0</v>
+      </c>
+      <c r="AM7" t="n" s="0">
+        <v>62200.0</v>
+      </c>
+      <c r="AN7" t="n" s="0">
+        <v>63000.0</v>
+      </c>
+      <c r="AO7" t="n" s="0">
+        <v>61800.0</v>
+      </c>
+      <c r="AP7" t="n" s="0">
+        <v>63000.0</v>
+      </c>
+      <c r="AQ7" t="n" s="0">
+        <v>63400.0</v>
+      </c>
+      <c r="AR7" t="n" s="0">
+        <v>66800.0</v>
+      </c>
+      <c r="AS7" t="n" s="0">
+        <v>66800.0</v>
+      </c>
+      <c r="AT7" t="n" s="0">
+        <v>62900.0</v>
+      </c>
+      <c r="AU7" t="n" s="0">
+        <v>64600.0</v>
+      </c>
+      <c r="AV7" t="n" s="0">
+        <v>66900.0</v>
+      </c>
+      <c r="AW7" t="n" s="0">
+        <v>63600.0</v>
+      </c>
+      <c r="AX7" t="n" s="0">
+        <v>63500.0</v>
+      </c>
+      <c r="AY7" t="n" s="0">
+        <v>63100.0</v>
+      </c>
+      <c r="AZ7" t="n" s="0">
+        <v>69100.0</v>
+      </c>
+      <c r="BA7" t="n" s="0">
+        <v>61300.0</v>
+      </c>
+      <c r="BB7" t="n" s="0">
+        <v>67100.0</v>
+      </c>
+      <c r="BC7" t="n" s="0">
+        <v>62700.0</v>
+      </c>
+      <c r="BD7" t="n" s="0">
+        <v>62900.0</v>
+      </c>
+      <c r="BE7" t="n" s="0">
+        <v>62200.0</v>
+      </c>
+      <c r="BF7" t="n" s="0">
+        <v>74200.0</v>
+      </c>
+      <c r="BG7" t="n" s="0">
+        <v>68400.0</v>
+      </c>
+      <c r="BH7" t="n" s="0">
+        <v>66200.0</v>
+      </c>
+      <c r="BI7" t="n" s="0">
+        <v>63500.0</v>
+      </c>
+      <c r="BJ7" t="n" s="0">
+        <v>62400.0</v>
+      </c>
+      <c r="BK7" t="n" s="0">
+        <v>62900.0</v>
+      </c>
+      <c r="BL7" t="n" s="0">
+        <v>64600.0</v>
+      </c>
+      <c r="BM7" t="n" s="0">
+        <v>62900.0</v>
+      </c>
+      <c r="BN7" t="n" s="0">
+        <v>63000.0</v>
+      </c>
+      <c r="BO7" t="n" s="0">
+        <v>133900.0</v>
+      </c>
+      <c r="BP7" t="n" s="0">
+        <v>99500.0</v>
+      </c>
+      <c r="BQ7" t="n" s="0">
+        <v>63500.0</v>
+      </c>
+      <c r="BR7" t="n" s="0">
+        <v>65300.0</v>
+      </c>
+      <c r="BS7" t="n" s="0">
+        <v>62500.0</v>
+      </c>
+      <c r="BT7" t="n" s="0">
+        <v>69400.0</v>
+      </c>
+      <c r="BU7" t="n" s="0">
+        <v>69100.0</v>
+      </c>
+      <c r="BV7" t="n" s="0">
+        <v>83500.0</v>
+      </c>
+      <c r="BW7" t="n" s="0">
+        <v>62500.0</v>
+      </c>
+      <c r="BX7" t="n" s="0">
+        <v>62500.0</v>
+      </c>
+      <c r="BY7" t="n" s="0">
+        <v>64800.0</v>
+      </c>
+      <c r="BZ7" t="n" s="0">
+        <v>61500.0</v>
+      </c>
+      <c r="CA7" t="n" s="0">
+        <v>62400.0</v>
+      </c>
+      <c r="CB7" t="n" s="0">
+        <v>62600.0</v>
+      </c>
+      <c r="CC7" t="n" s="0">
+        <v>63900.0</v>
+      </c>
+      <c r="CD7" t="n" s="0">
+        <v>62800.0</v>
+      </c>
+      <c r="CE7" t="n" s="0">
+        <v>62900.0</v>
+      </c>
+      <c r="CF7" t="n" s="0">
+        <v>62700.0</v>
+      </c>
+      <c r="CG7" t="n" s="0">
+        <v>62600.0</v>
+      </c>
+      <c r="CH7" t="n" s="0">
+        <v>64200.0</v>
+      </c>
+      <c r="CI7" t="n" s="0">
+        <v>62900.0</v>
+      </c>
+      <c r="CJ7" t="n" s="0">
+        <v>63800.0</v>
+      </c>
+      <c r="CK7" t="n" s="0">
+        <v>62400.0</v>
+      </c>
+      <c r="CL7" t="n" s="0">
+        <v>61100.0</v>
+      </c>
+      <c r="CM7" t="n" s="0">
+        <v>63000.0</v>
+      </c>
+      <c r="CN7" t="n" s="0">
+        <v>62900.0</v>
+      </c>
+      <c r="CO7" t="n" s="0">
+        <v>67200.0</v>
+      </c>
+      <c r="CP7" t="n" s="0">
+        <v>62600.0</v>
+      </c>
+      <c r="CQ7" t="n" s="0">
+        <v>64000.0</v>
+      </c>
+      <c r="CR7" t="n" s="0">
+        <v>64500.0</v>
+      </c>
+      <c r="CS7" t="n" s="0">
+        <v>62400.0</v>
+      </c>
+      <c r="CT7" t="n" s="0">
+        <v>63500.0</v>
+      </c>
+      <c r="CU7" t="n" s="0">
+        <v>63900.0</v>
+      </c>
+      <c r="CV7" t="n" s="0">
+        <v>119900.0</v>
+      </c>
+      <c r="CW7" t="n" s="0">
+        <v>120400.0</v>
+      </c>
+      <c r="CX7" t="n" s="0">
+        <v>120400.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B8" t="n" s="0">
+        <v>500.0</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>233400.0</v>
+      </c>
+      <c r="D8" t="n" s="0">
+        <v>92200.0</v>
+      </c>
+      <c r="E8" t="n" s="0">
+        <v>84400.0</v>
+      </c>
+      <c r="F8" t="n" s="0">
+        <v>51500.0</v>
+      </c>
+      <c r="G8" t="n" s="0">
+        <v>91300.0</v>
+      </c>
+      <c r="H8" t="n" s="0">
+        <v>167500.0</v>
+      </c>
+      <c r="I8" t="n" s="0">
+        <v>62900.0</v>
+      </c>
+      <c r="J8" t="n" s="0">
+        <v>221700.0</v>
+      </c>
+      <c r="K8" t="n" s="0">
+        <v>52800.0</v>
+      </c>
+      <c r="L8" t="n" s="0">
+        <v>75900.0</v>
+      </c>
+      <c r="M8" t="n" s="0">
+        <v>44900.0</v>
+      </c>
+      <c r="N8" t="n" s="0">
+        <v>111200.0</v>
+      </c>
+      <c r="O8" t="n" s="0">
+        <v>63400.0</v>
+      </c>
+      <c r="P8" t="n" s="0">
+        <v>61600.0</v>
+      </c>
+      <c r="Q8" t="n" s="0">
+        <v>46900.0</v>
+      </c>
+      <c r="R8" t="n" s="0">
+        <v>37800.0</v>
+      </c>
+      <c r="S8" t="n" s="0">
+        <v>34300.0</v>
+      </c>
+      <c r="T8" t="n" s="0">
+        <v>64300.0</v>
+      </c>
+      <c r="U8" t="n" s="0">
+        <v>44700.0</v>
+      </c>
+      <c r="V8" t="n" s="0">
+        <v>35800.0</v>
+      </c>
+      <c r="W8" t="n" s="0">
+        <v>37300.0</v>
+      </c>
+      <c r="X8" t="n" s="0">
+        <v>35300.0</v>
+      </c>
+      <c r="Y8" t="n" s="0">
+        <v>41600.0</v>
+      </c>
+      <c r="Z8" t="n" s="0">
+        <v>40500.0</v>
+      </c>
+      <c r="AA8" t="n" s="0">
+        <v>35800.0</v>
+      </c>
+      <c r="AB8" t="n" s="0">
+        <v>36800.0</v>
+      </c>
+      <c r="AC8" t="n" s="0">
+        <v>36100.0</v>
+      </c>
+      <c r="AD8" t="n" s="0">
+        <v>45200.0</v>
+      </c>
+      <c r="AE8" t="n" s="0">
+        <v>63600.0</v>
+      </c>
+      <c r="AF8" t="n" s="0">
+        <v>59100.0</v>
+      </c>
+      <c r="AG8" t="n" s="0">
+        <v>40300.0</v>
+      </c>
+      <c r="AH8" t="n" s="0">
+        <v>36500.0</v>
+      </c>
+      <c r="AI8" t="n" s="0">
+        <v>36000.0</v>
+      </c>
+      <c r="AJ8" t="n" s="0">
+        <v>67800.0</v>
+      </c>
+      <c r="AK8" t="n" s="0">
+        <v>39500.0</v>
+      </c>
+      <c r="AL8" t="n" s="0">
+        <v>51600.0</v>
+      </c>
+      <c r="AM8" t="n" s="0">
+        <v>41900.0</v>
+      </c>
+      <c r="AN8" t="n" s="0">
+        <v>36100.0</v>
+      </c>
+      <c r="AO8" t="n" s="0">
+        <v>39300.0</v>
+      </c>
+      <c r="AP8" t="n" s="0">
+        <v>36500.0</v>
+      </c>
+      <c r="AQ8" t="n" s="0">
+        <v>36200.0</v>
+      </c>
+      <c r="AR8" t="n" s="0">
+        <v>36900.0</v>
+      </c>
+      <c r="AS8" t="n" s="0">
+        <v>44600.0</v>
+      </c>
+      <c r="AT8" t="n" s="0">
+        <v>40900.0</v>
+      </c>
+      <c r="AU8" t="n" s="0">
+        <v>38400.0</v>
+      </c>
+      <c r="AV8" t="n" s="0">
+        <v>41400.0</v>
+      </c>
+      <c r="AW8" t="n" s="0">
+        <v>35900.0</v>
+      </c>
+      <c r="AX8" t="n" s="0">
+        <v>43700.0</v>
+      </c>
+      <c r="AY8" t="n" s="0">
+        <v>41900.0</v>
+      </c>
+      <c r="AZ8" t="n" s="0">
+        <v>40900.0</v>
+      </c>
+      <c r="BA8" t="n" s="0">
+        <v>44100.0</v>
+      </c>
+      <c r="BB8" t="n" s="0">
+        <v>47000.0</v>
+      </c>
+      <c r="BC8" t="n" s="0">
+        <v>41500.0</v>
+      </c>
+      <c r="BD8" t="n" s="0">
+        <v>42400.0</v>
+      </c>
+      <c r="BE8" t="n" s="0">
+        <v>41500.0</v>
+      </c>
+      <c r="BF8" t="n" s="0">
+        <v>58300.0</v>
+      </c>
+      <c r="BG8" t="n" s="0">
+        <v>43900.0</v>
+      </c>
+      <c r="BH8" t="n" s="0">
+        <v>43300.0</v>
+      </c>
+      <c r="BI8" t="n" s="0">
+        <v>43600.0</v>
+      </c>
+      <c r="BJ8" t="n" s="0">
+        <v>41300.0</v>
+      </c>
+      <c r="BK8" t="n" s="0">
+        <v>40900.0</v>
+      </c>
+      <c r="BL8" t="n" s="0">
+        <v>42800.0</v>
+      </c>
+      <c r="BM8" t="n" s="0">
+        <v>43300.0</v>
+      </c>
+      <c r="BN8" t="n" s="0">
+        <v>42200.0</v>
+      </c>
+      <c r="BO8" t="n" s="0">
+        <v>73600.0</v>
+      </c>
+      <c r="BP8" t="n" s="0">
+        <v>49000.0</v>
+      </c>
+      <c r="BQ8" t="n" s="0">
+        <v>42600.0</v>
+      </c>
+      <c r="BR8" t="n" s="0">
+        <v>122300.0</v>
+      </c>
+      <c r="BS8" t="n" s="0">
+        <v>39800.0</v>
+      </c>
+      <c r="BT8" t="n" s="0">
+        <v>47600.0</v>
+      </c>
+      <c r="BU8" t="n" s="0">
+        <v>51600.0</v>
+      </c>
+      <c r="BV8" t="n" s="0">
+        <v>50500.0</v>
+      </c>
+      <c r="BW8" t="n" s="0">
+        <v>42600.0</v>
+      </c>
+      <c r="BX8" t="n" s="0">
+        <v>50200.0</v>
+      </c>
+      <c r="BY8" t="n" s="0">
+        <v>35000.0</v>
+      </c>
+      <c r="BZ8" t="n" s="0">
+        <v>36000.0</v>
+      </c>
+      <c r="CA8" t="n" s="0">
+        <v>34400.0</v>
+      </c>
+      <c r="CB8" t="n" s="0">
+        <v>35500.0</v>
+      </c>
+      <c r="CC8" t="n" s="0">
+        <v>35400.0</v>
+      </c>
+      <c r="CD8" t="n" s="0">
+        <v>34700.0</v>
+      </c>
+      <c r="CE8" t="n" s="0">
+        <v>36300.0</v>
+      </c>
+      <c r="CF8" t="n" s="0">
+        <v>34700.0</v>
+      </c>
+      <c r="CG8" t="n" s="0">
+        <v>37400.0</v>
+      </c>
+      <c r="CH8" t="n" s="0">
+        <v>34700.0</v>
+      </c>
+      <c r="CI8" t="n" s="0">
+        <v>42800.0</v>
+      </c>
+      <c r="CJ8" t="n" s="0">
+        <v>35400.0</v>
+      </c>
+      <c r="CK8" t="n" s="0">
+        <v>34900.0</v>
+      </c>
+      <c r="CL8" t="n" s="0">
+        <v>34500.0</v>
+      </c>
+      <c r="CM8" t="n" s="0">
+        <v>35900.0</v>
+      </c>
+      <c r="CN8" t="n" s="0">
+        <v>37000.0</v>
+      </c>
+      <c r="CO8" t="n" s="0">
+        <v>47000.0</v>
+      </c>
+      <c r="CP8" t="n" s="0">
+        <v>36900.0</v>
+      </c>
+      <c r="CQ8" t="n" s="0">
+        <v>37700.0</v>
+      </c>
+      <c r="CR8" t="n" s="0">
+        <v>35300.0</v>
+      </c>
+      <c r="CS8" t="n" s="0">
+        <v>34500.0</v>
+      </c>
+      <c r="CT8" t="n" s="0">
+        <v>34700.0</v>
+      </c>
+      <c r="CU8" t="n" s="0">
+        <v>36100.0</v>
+      </c>
+      <c r="CV8" t="n" s="0">
+        <v>56500.0</v>
+      </c>
+      <c r="CW8" t="n" s="0">
+        <v>60100.0</v>
+      </c>
+      <c r="CX8" t="n" s="0">
+        <v>58600.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B9" t="n" s="0">
+        <v>500.0</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>223600.0</v>
+      </c>
+      <c r="D9" t="n" s="0">
+        <v>94200.0</v>
+      </c>
+      <c r="E9" t="n" s="0">
+        <v>67900.0</v>
+      </c>
+      <c r="F9" t="n" s="0">
+        <v>50700.0</v>
+      </c>
+      <c r="G9" t="n" s="0">
+        <v>81400.0</v>
+      </c>
+      <c r="H9" t="n" s="0">
+        <v>116600.0</v>
+      </c>
+      <c r="I9" t="n" s="0">
+        <v>64700.0</v>
+      </c>
+      <c r="J9" t="n" s="0">
+        <v>73100.0</v>
+      </c>
+      <c r="K9" t="n" s="0">
+        <v>46900.0</v>
+      </c>
+      <c r="L9" t="n" s="0">
+        <v>71600.0</v>
+      </c>
+      <c r="M9" t="n" s="0">
+        <v>38800.0</v>
+      </c>
+      <c r="N9" t="n" s="0">
+        <v>64800.0</v>
+      </c>
+      <c r="O9" t="n" s="0">
+        <v>87200.0</v>
+      </c>
+      <c r="P9" t="n" s="0">
+        <v>55300.0</v>
+      </c>
+      <c r="Q9" t="n" s="0">
+        <v>47300.0</v>
+      </c>
+      <c r="R9" t="n" s="0">
+        <v>36000.0</v>
+      </c>
+      <c r="S9" t="n" s="0">
+        <v>33300.0</v>
+      </c>
+      <c r="T9" t="n" s="0">
+        <v>69000.0</v>
+      </c>
+      <c r="U9" t="n" s="0">
+        <v>34800.0</v>
+      </c>
+      <c r="V9" t="n" s="0">
+        <v>35800.0</v>
+      </c>
+      <c r="W9" t="n" s="0">
+        <v>36900.0</v>
+      </c>
+      <c r="X9" t="n" s="0">
+        <v>38100.0</v>
+      </c>
+      <c r="Y9" t="n" s="0">
+        <v>38600.0</v>
+      </c>
+      <c r="Z9" t="n" s="0">
+        <v>36700.0</v>
+      </c>
+      <c r="AA9" t="n" s="0">
+        <v>35200.0</v>
+      </c>
+      <c r="AB9" t="n" s="0">
+        <v>35400.0</v>
+      </c>
+      <c r="AC9" t="n" s="0">
+        <v>35300.0</v>
+      </c>
+      <c r="AD9" t="n" s="0">
+        <v>41600.0</v>
+      </c>
+      <c r="AE9" t="n" s="0">
+        <v>82100.0</v>
+      </c>
+      <c r="AF9" t="n" s="0">
+        <v>63000.0</v>
+      </c>
+      <c r="AG9" t="n" s="0">
+        <v>36400.0</v>
+      </c>
+      <c r="AH9" t="n" s="0">
+        <v>35900.0</v>
+      </c>
+      <c r="AI9" t="n" s="0">
+        <v>37400.0</v>
+      </c>
+      <c r="AJ9" t="n" s="0">
+        <v>61500.0</v>
+      </c>
+      <c r="AK9" t="n" s="0">
+        <v>39600.0</v>
+      </c>
+      <c r="AL9" t="n" s="0">
+        <v>42600.0</v>
+      </c>
+      <c r="AM9" t="n" s="0">
+        <v>41100.0</v>
+      </c>
+      <c r="AN9" t="n" s="0">
+        <v>34400.0</v>
+      </c>
+      <c r="AO9" t="n" s="0">
+        <v>34500.0</v>
+      </c>
+      <c r="AP9" t="n" s="0">
+        <v>38200.0</v>
+      </c>
+      <c r="AQ9" t="n" s="0">
+        <v>36500.0</v>
+      </c>
+      <c r="AR9" t="n" s="0">
+        <v>36900.0</v>
+      </c>
+      <c r="AS9" t="n" s="0">
+        <v>48100.0</v>
+      </c>
+      <c r="AT9" t="n" s="0">
+        <v>39700.0</v>
+      </c>
+      <c r="AU9" t="n" s="0">
+        <v>6493500.0</v>
+      </c>
+      <c r="AV9" t="n" s="0">
+        <v>34600.0</v>
+      </c>
+      <c r="AW9" t="n" s="0">
+        <v>36600.0</v>
+      </c>
+      <c r="AX9" t="n" s="0">
+        <v>55800.0</v>
+      </c>
+      <c r="AY9" t="n" s="0">
+        <v>40000.0</v>
+      </c>
+      <c r="AZ9" t="n" s="0">
+        <v>40600.0</v>
+      </c>
+      <c r="BA9" t="n" s="0">
+        <v>41600.0</v>
+      </c>
+      <c r="BB9" t="n" s="0">
+        <v>43800.0</v>
+      </c>
+      <c r="BC9" t="n" s="0">
+        <v>92700.0</v>
+      </c>
+      <c r="BD9" t="n" s="0">
+        <v>40800.0</v>
+      </c>
+      <c r="BE9" t="n" s="0">
+        <v>42900.0</v>
+      </c>
+      <c r="BF9" t="n" s="0">
+        <v>55000.0</v>
+      </c>
+      <c r="BG9" t="n" s="0">
+        <v>41500.0</v>
+      </c>
+      <c r="BH9" t="n" s="0">
+        <v>40700.0</v>
+      </c>
+      <c r="BI9" t="n" s="0">
+        <v>42900.0</v>
+      </c>
+      <c r="BJ9" t="n" s="0">
+        <v>42400.0</v>
+      </c>
+      <c r="BK9" t="n" s="0">
+        <v>42700.0</v>
+      </c>
+      <c r="BL9" t="n" s="0">
+        <v>41200.0</v>
+      </c>
+      <c r="BM9" t="n" s="0">
+        <v>43000.0</v>
+      </c>
+      <c r="BN9" t="n" s="0">
+        <v>41100.0</v>
+      </c>
+      <c r="BO9" t="n" s="0">
+        <v>53200.0</v>
+      </c>
+      <c r="BP9" t="n" s="0">
+        <v>43800.0</v>
+      </c>
+      <c r="BQ9" t="n" s="0">
+        <v>44600.0</v>
+      </c>
+      <c r="BR9" t="n" s="0">
+        <v>48700.0</v>
+      </c>
+      <c r="BS9" t="n" s="0">
+        <v>43500.0</v>
+      </c>
+      <c r="BT9" t="n" s="0">
+        <v>45600.0</v>
+      </c>
+      <c r="BU9" t="n" s="0">
+        <v>49400.0</v>
+      </c>
+      <c r="BV9" t="n" s="0">
+        <v>46500.0</v>
+      </c>
+      <c r="BW9" t="n" s="0">
+        <v>40600.0</v>
+      </c>
+      <c r="BX9" t="n" s="0">
+        <v>43300.0</v>
+      </c>
+      <c r="BY9" t="n" s="0">
+        <v>35400.0</v>
+      </c>
+      <c r="BZ9" t="n" s="0">
+        <v>88200.0</v>
+      </c>
+      <c r="CA9" t="n" s="0">
+        <v>35700.0</v>
+      </c>
+      <c r="CB9" t="n" s="0">
+        <v>35300.0</v>
+      </c>
+      <c r="CC9" t="n" s="0">
+        <v>35300.0</v>
+      </c>
+      <c r="CD9" t="n" s="0">
+        <v>35600.0</v>
+      </c>
+      <c r="CE9" t="n" s="0">
+        <v>36400.0</v>
+      </c>
+      <c r="CF9" t="n" s="0">
+        <v>34700.0</v>
+      </c>
+      <c r="CG9" t="n" s="0">
+        <v>52000.0</v>
+      </c>
+      <c r="CH9" t="n" s="0">
+        <v>35500.0</v>
+      </c>
+      <c r="CI9" t="n" s="0">
+        <v>34500.0</v>
+      </c>
+      <c r="CJ9" t="n" s="0">
+        <v>34700.0</v>
+      </c>
+      <c r="CK9" t="n" s="0">
+        <v>35200.0</v>
+      </c>
+      <c r="CL9" t="n" s="0">
+        <v>36500.0</v>
+      </c>
+      <c r="CM9" t="n" s="0">
+        <v>34400.0</v>
+      </c>
+      <c r="CN9" t="n" s="0">
+        <v>38400.0</v>
+      </c>
+      <c r="CO9" t="n" s="0">
+        <v>36400.0</v>
+      </c>
+      <c r="CP9" t="n" s="0">
+        <v>35900.0</v>
+      </c>
+      <c r="CQ9" t="n" s="0">
+        <v>35600.0</v>
+      </c>
+      <c r="CR9" t="n" s="0">
+        <v>35200.0</v>
+      </c>
+      <c r="CS9" t="n" s="0">
+        <v>34300.0</v>
+      </c>
+      <c r="CT9" t="n" s="0">
+        <v>34600.0</v>
+      </c>
+      <c r="CU9" t="n" s="0">
+        <v>35600.0</v>
+      </c>
+      <c r="CV9" t="n" s="0">
+        <v>57600.0</v>
+      </c>
+      <c r="CW9" t="n" s="0">
+        <v>59300.0</v>
+      </c>
+      <c r="CX9" t="n" s="0">
+        <v>58000.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B10" t="n" s="0">
+        <v>500.0</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>260000.0</v>
+      </c>
+      <c r="D10" t="n" s="0">
+        <v>110400.0</v>
+      </c>
+      <c r="E10" t="n" s="0">
+        <v>85600.0</v>
+      </c>
+      <c r="F10" t="n" s="0">
+        <v>71100.0</v>
+      </c>
+      <c r="G10" t="n" s="0">
+        <v>119000.0</v>
+      </c>
+      <c r="H10" t="n" s="0">
+        <v>76600.0</v>
+      </c>
+      <c r="I10" t="n" s="0">
+        <v>74500.0</v>
+      </c>
+      <c r="J10" t="n" s="0">
+        <v>74100.0</v>
+      </c>
+      <c r="K10" t="n" s="0">
+        <v>55900.0</v>
+      </c>
+      <c r="L10" t="n" s="0">
+        <v>121700.0</v>
+      </c>
+      <c r="M10" t="n" s="0">
+        <v>54700.0</v>
+      </c>
+      <c r="N10" t="n" s="0">
+        <v>165200.0</v>
+      </c>
+      <c r="O10" t="n" s="0">
+        <v>77200.0</v>
+      </c>
+      <c r="P10" t="n" s="0">
+        <v>74600.0</v>
+      </c>
+      <c r="Q10" t="n" s="0">
+        <v>70500.0</v>
+      </c>
+      <c r="R10" t="n" s="0">
+        <v>46600.0</v>
+      </c>
+      <c r="S10" t="n" s="0">
+        <v>48400.0</v>
+      </c>
+      <c r="T10" t="n" s="0">
+        <v>1.04135E7</v>
+      </c>
+      <c r="U10" t="n" s="0">
+        <v>45700.0</v>
+      </c>
+      <c r="V10" t="n" s="0">
+        <v>48500.0</v>
+      </c>
+      <c r="W10" t="n" s="0">
+        <v>49300.0</v>
+      </c>
+      <c r="X10" t="n" s="0">
+        <v>45300.0</v>
+      </c>
+      <c r="Y10" t="n" s="0">
+        <v>55600.0</v>
+      </c>
+      <c r="Z10" t="n" s="0">
+        <v>47100.0</v>
+      </c>
+      <c r="AA10" t="n" s="0">
+        <v>50700.0</v>
+      </c>
+      <c r="AB10" t="n" s="0">
+        <v>50000.0</v>
+      </c>
+      <c r="AC10" t="n" s="0">
+        <v>47300.0</v>
+      </c>
+      <c r="AD10" t="n" s="0">
+        <v>70400.0</v>
+      </c>
+      <c r="AE10" t="n" s="0">
+        <v>70000.0</v>
+      </c>
+      <c r="AF10" t="n" s="0">
+        <v>67600.0</v>
+      </c>
+      <c r="AG10" t="n" s="0">
+        <v>46900.0</v>
+      </c>
+      <c r="AH10" t="n" s="0">
+        <v>194800.0</v>
+      </c>
+      <c r="AI10" t="n" s="0">
+        <v>78900.0</v>
+      </c>
+      <c r="AJ10" t="n" s="0">
+        <v>74500.0</v>
+      </c>
+      <c r="AK10" t="n" s="0">
+        <v>53900.0</v>
+      </c>
+      <c r="AL10" t="n" s="0">
+        <v>57100.0</v>
+      </c>
+      <c r="AM10" t="n" s="0">
+        <v>61900.0</v>
+      </c>
+      <c r="AN10" t="n" s="0">
+        <v>47200.0</v>
+      </c>
+      <c r="AO10" t="n" s="0">
+        <v>47900.0</v>
+      </c>
+      <c r="AP10" t="n" s="0">
+        <v>49300.0</v>
+      </c>
+      <c r="AQ10" t="n" s="0">
+        <v>50400.0</v>
+      </c>
+      <c r="AR10" t="n" s="0">
+        <v>49500.0</v>
+      </c>
+      <c r="AS10" t="n" s="0">
+        <v>58900.0</v>
+      </c>
+      <c r="AT10" t="n" s="0">
+        <v>62500.0</v>
+      </c>
+      <c r="AU10" t="n" s="0">
+        <v>69800.0</v>
+      </c>
+      <c r="AV10" t="n" s="0">
+        <v>47200.0</v>
+      </c>
+      <c r="AW10" t="n" s="0">
+        <v>47600.0</v>
+      </c>
+      <c r="AX10" t="n" s="0">
+        <v>55700.0</v>
+      </c>
+      <c r="AY10" t="n" s="0">
+        <v>54900.0</v>
+      </c>
+      <c r="AZ10" t="n" s="0">
+        <v>53500.0</v>
+      </c>
+      <c r="BA10" t="n" s="0">
+        <v>55900.0</v>
+      </c>
+      <c r="BB10" t="n" s="0">
+        <v>58700.0</v>
+      </c>
+      <c r="BC10" t="n" s="0">
+        <v>55300.0</v>
+      </c>
+      <c r="BD10" t="n" s="0">
+        <v>53200.0</v>
+      </c>
+      <c r="BE10" t="n" s="0">
+        <v>59400.0</v>
+      </c>
+      <c r="BF10" t="n" s="0">
+        <v>74500.0</v>
+      </c>
+      <c r="BG10" t="n" s="0">
+        <v>56900.0</v>
+      </c>
+      <c r="BH10" t="n" s="0">
+        <v>53700.0</v>
+      </c>
+      <c r="BI10" t="n" s="0">
+        <v>58000.0</v>
+      </c>
+      <c r="BJ10" t="n" s="0">
+        <v>54100.0</v>
+      </c>
+      <c r="BK10" t="n" s="0">
+        <v>54300.0</v>
+      </c>
+      <c r="BL10" t="n" s="0">
+        <v>82700.0</v>
+      </c>
+      <c r="BM10" t="n" s="0">
+        <v>55100.0</v>
+      </c>
+      <c r="BN10" t="n" s="0">
+        <v>77600.0</v>
+      </c>
+      <c r="BO10" t="n" s="0">
+        <v>60200.0</v>
+      </c>
+      <c r="BP10" t="n" s="0">
+        <v>58900.0</v>
+      </c>
+      <c r="BQ10" t="n" s="0">
+        <v>138600.0</v>
+      </c>
+      <c r="BR10" t="n" s="0">
+        <v>61800.0</v>
+      </c>
+      <c r="BS10" t="n" s="0">
+        <v>59400.0</v>
+      </c>
+      <c r="BT10" t="n" s="0">
+        <v>64900.0</v>
+      </c>
+      <c r="BU10" t="n" s="0">
+        <v>87900.0</v>
+      </c>
+      <c r="BV10" t="n" s="0">
+        <v>60200.0</v>
+      </c>
+      <c r="BW10" t="n" s="0">
+        <v>57800.0</v>
+      </c>
+      <c r="BX10" t="n" s="0">
+        <v>56100.0</v>
+      </c>
+      <c r="BY10" t="n" s="0">
+        <v>48100.0</v>
+      </c>
+      <c r="BZ10" t="n" s="0">
+        <v>46400.0</v>
+      </c>
+      <c r="CA10" t="n" s="0">
+        <v>46200.0</v>
+      </c>
+      <c r="CB10" t="n" s="0">
+        <v>47300.0</v>
+      </c>
+      <c r="CC10" t="n" s="0">
+        <v>47100.0</v>
+      </c>
+      <c r="CD10" t="n" s="0">
+        <v>49200.0</v>
+      </c>
+      <c r="CE10" t="n" s="0">
+        <v>47900.0</v>
+      </c>
+      <c r="CF10" t="n" s="0">
+        <v>60800.0</v>
+      </c>
+      <c r="CG10" t="n" s="0">
+        <v>48000.0</v>
+      </c>
+      <c r="CH10" t="n" s="0">
+        <v>48000.0</v>
+      </c>
+      <c r="CI10" t="n" s="0">
+        <v>47300.0</v>
+      </c>
+      <c r="CJ10" t="n" s="0">
+        <v>47600.0</v>
+      </c>
+      <c r="CK10" t="n" s="0">
+        <v>47100.0</v>
+      </c>
+      <c r="CL10" t="n" s="0">
+        <v>48600.0</v>
+      </c>
+      <c r="CM10" t="n" s="0">
+        <v>48600.0</v>
+      </c>
+      <c r="CN10" t="n" s="0">
+        <v>50700.0</v>
+      </c>
+      <c r="CO10" t="n" s="0">
+        <v>49500.0</v>
+      </c>
+      <c r="CP10" t="n" s="0">
+        <v>51400.0</v>
+      </c>
+      <c r="CQ10" t="n" s="0">
+        <v>49500.0</v>
+      </c>
+      <c r="CR10" t="n" s="0">
+        <v>49900.0</v>
+      </c>
+      <c r="CS10" t="n" s="0">
+        <v>46500.0</v>
+      </c>
+      <c r="CT10" t="n" s="0">
+        <v>48500.0</v>
+      </c>
+      <c r="CU10" t="n" s="0">
+        <v>48600.0</v>
+      </c>
+      <c r="CV10" t="n" s="0">
+        <v>63200.0</v>
+      </c>
+      <c r="CW10" t="n" s="0">
+        <v>66500.0</v>
+      </c>
+      <c r="CX10" t="n" s="0">
+        <v>73400.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B11" t="n" s="0">
+        <v>500.0</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>203700.0</v>
+      </c>
+      <c r="D11" t="n" s="0">
+        <v>111600.0</v>
+      </c>
+      <c r="E11" t="n" s="0">
+        <v>87700.0</v>
+      </c>
+      <c r="F11" t="n" s="0">
+        <v>61100.0</v>
+      </c>
+      <c r="G11" t="n" s="0">
+        <v>112800.0</v>
+      </c>
+      <c r="H11" t="n" s="0">
+        <v>87500.0</v>
+      </c>
+      <c r="I11" t="n" s="0">
+        <v>69400.0</v>
+      </c>
+      <c r="J11" t="n" s="0">
+        <v>76200.0</v>
+      </c>
+      <c r="K11" t="n" s="0">
+        <v>51700.0</v>
+      </c>
+      <c r="L11" t="n" s="0">
+        <v>106900.0</v>
+      </c>
+      <c r="M11" t="n" s="0">
+        <v>53400.0</v>
+      </c>
+      <c r="N11" t="n" s="0">
+        <v>81800.0</v>
+      </c>
+      <c r="O11" t="n" s="0">
+        <v>110000.0</v>
+      </c>
+      <c r="P11" t="n" s="0">
+        <v>80100.0</v>
+      </c>
+      <c r="Q11" t="n" s="0">
+        <v>64900.0</v>
+      </c>
+      <c r="R11" t="n" s="0">
+        <v>47400.0</v>
+      </c>
+      <c r="S11" t="n" s="0">
+        <v>48700.0</v>
+      </c>
+      <c r="T11" t="n" s="0">
+        <v>59300.0</v>
+      </c>
+      <c r="U11" t="n" s="0">
+        <v>47900.0</v>
+      </c>
+      <c r="V11" t="n" s="0">
+        <v>48000.0</v>
+      </c>
+      <c r="W11" t="n" s="0">
+        <v>50900.0</v>
+      </c>
+      <c r="X11" t="n" s="0">
+        <v>47400.0</v>
+      </c>
+      <c r="Y11" t="n" s="0">
+        <v>47100.0</v>
+      </c>
+      <c r="Z11" t="n" s="0">
+        <v>48000.0</v>
+      </c>
+      <c r="AA11" t="n" s="0">
+        <v>47700.0</v>
+      </c>
+      <c r="AB11" t="n" s="0">
+        <v>50100.0</v>
+      </c>
+      <c r="AC11" t="n" s="0">
+        <v>48100.0</v>
+      </c>
+      <c r="AD11" t="n" s="0">
+        <v>68800.0</v>
+      </c>
+      <c r="AE11" t="n" s="0">
+        <v>75400.0</v>
+      </c>
+      <c r="AF11" t="n" s="0">
+        <v>68000.0</v>
+      </c>
+      <c r="AG11" t="n" s="0">
+        <v>51400.0</v>
+      </c>
+      <c r="AH11" t="n" s="0">
+        <v>55900.0</v>
+      </c>
+      <c r="AI11" t="n" s="0">
+        <v>70800.0</v>
+      </c>
+      <c r="AJ11" t="n" s="0">
+        <v>70200.0</v>
+      </c>
+      <c r="AK11" t="n" s="0">
+        <v>53600.0</v>
+      </c>
+      <c r="AL11" t="n" s="0">
+        <v>58400.0</v>
+      </c>
+      <c r="AM11" t="n" s="0">
+        <v>63800.0</v>
+      </c>
+      <c r="AN11" t="n" s="0">
+        <v>46800.0</v>
+      </c>
+      <c r="AO11" t="n" s="0">
+        <v>46900.0</v>
+      </c>
+      <c r="AP11" t="n" s="0">
+        <v>51600.0</v>
+      </c>
+      <c r="AQ11" t="n" s="0">
+        <v>48800.0</v>
+      </c>
+      <c r="AR11" t="n" s="0">
+        <v>50300.0</v>
+      </c>
+      <c r="AS11" t="n" s="0">
+        <v>60600.0</v>
+      </c>
+      <c r="AT11" t="n" s="0">
+        <v>73100.0</v>
+      </c>
+      <c r="AU11" t="n" s="0">
+        <v>50100.0</v>
+      </c>
+      <c r="AV11" t="n" s="0">
+        <v>47500.0</v>
+      </c>
+      <c r="AW11" t="n" s="0">
+        <v>46900.0</v>
+      </c>
+      <c r="AX11" t="n" s="0">
+        <v>56800.0</v>
+      </c>
+      <c r="AY11" t="n" s="0">
+        <v>58900.0</v>
+      </c>
+      <c r="AZ11" t="n" s="0">
+        <v>51000.0</v>
+      </c>
+      <c r="BA11" t="n" s="0">
+        <v>55500.0</v>
+      </c>
+      <c r="BB11" t="n" s="0">
+        <v>57300.0</v>
+      </c>
+      <c r="BC11" t="n" s="0">
+        <v>53400.0</v>
+      </c>
+      <c r="BD11" t="n" s="0">
+        <v>69500.0</v>
+      </c>
+      <c r="BE11" t="n" s="0">
+        <v>57200.0</v>
+      </c>
+      <c r="BF11" t="n" s="0">
+        <v>70000.0</v>
+      </c>
+      <c r="BG11" t="n" s="0">
+        <v>58100.0</v>
+      </c>
+      <c r="BH11" t="n" s="0">
+        <v>54200.0</v>
+      </c>
+      <c r="BI11" t="n" s="0">
+        <v>55000.0</v>
+      </c>
+      <c r="BJ11" t="n" s="0">
+        <v>58500.0</v>
+      </c>
+      <c r="BK11" t="n" s="0">
+        <v>55500.0</v>
+      </c>
+      <c r="BL11" t="n" s="0">
+        <v>60400.0</v>
+      </c>
+      <c r="BM11" t="n" s="0">
+        <v>70100.0</v>
+      </c>
+      <c r="BN11" t="n" s="0">
+        <v>59800.0</v>
+      </c>
+      <c r="BO11" t="n" s="0">
+        <v>57200.0</v>
+      </c>
+      <c r="BP11" t="n" s="0">
+        <v>58500.0</v>
+      </c>
+      <c r="BQ11" t="n" s="0">
+        <v>100800.0</v>
+      </c>
+      <c r="BR11" t="n" s="0">
+        <v>61400.0</v>
+      </c>
+      <c r="BS11" t="n" s="0">
+        <v>59400.0</v>
+      </c>
+      <c r="BT11" t="n" s="0">
+        <v>131100.0</v>
+      </c>
+      <c r="BU11" t="n" s="0">
+        <v>58200.0</v>
+      </c>
+      <c r="BV11" t="n" s="0">
+        <v>58500.0</v>
+      </c>
+      <c r="BW11" t="n" s="0">
+        <v>60500.0</v>
+      </c>
+      <c r="BX11" t="n" s="0">
+        <v>59600.0</v>
+      </c>
+      <c r="BY11" t="n" s="0">
+        <v>49000.0</v>
+      </c>
+      <c r="BZ11" t="n" s="0">
+        <v>47400.0</v>
+      </c>
+      <c r="CA11" t="n" s="0">
+        <v>44900.0</v>
+      </c>
+      <c r="CB11" t="n" s="0">
+        <v>48200.0</v>
+      </c>
+      <c r="CC11" t="n" s="0">
+        <v>48200.0</v>
+      </c>
+      <c r="CD11" t="n" s="0">
+        <v>49300.0</v>
+      </c>
+      <c r="CE11" t="n" s="0">
+        <v>49900.0</v>
+      </c>
+      <c r="CF11" t="n" s="0">
+        <v>46600.0</v>
+      </c>
+      <c r="CG11" t="n" s="0">
+        <v>49100.0</v>
+      </c>
+      <c r="CH11" t="n" s="0">
+        <v>48100.0</v>
+      </c>
+      <c r="CI11" t="n" s="0">
+        <v>46800.0</v>
+      </c>
+      <c r="CJ11" t="n" s="0">
+        <v>48400.0</v>
+      </c>
+      <c r="CK11" t="n" s="0">
+        <v>46700.0</v>
+      </c>
+      <c r="CL11" t="n" s="0">
+        <v>49900.0</v>
+      </c>
+      <c r="CM11" t="n" s="0">
+        <v>49900.0</v>
+      </c>
+      <c r="CN11" t="n" s="0">
+        <v>47900.0</v>
+      </c>
+      <c r="CO11" t="n" s="0">
+        <v>53400.0</v>
+      </c>
+      <c r="CP11" t="n" s="0">
+        <v>48300.0</v>
+      </c>
+      <c r="CQ11" t="n" s="0">
+        <v>49400.0</v>
+      </c>
+      <c r="CR11" t="n" s="0">
+        <v>47800.0</v>
+      </c>
+      <c r="CS11" t="n" s="0">
+        <v>51600.0</v>
+      </c>
+      <c r="CT11" t="n" s="0">
+        <v>48700.0</v>
+      </c>
+      <c r="CU11" t="n" s="0">
+        <v>110300.0</v>
+      </c>
+      <c r="CV11" t="n" s="0">
+        <v>63900.0</v>
+      </c>
+      <c r="CW11" t="n" s="0">
+        <v>70500.0</v>
+      </c>
+      <c r="CX11" t="n" s="0">
+        <v>68400.0</v>
       </c>
     </row>
   </sheetData>
